--- a/output/upload/S00026_2208_간편가입_제로백H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2208_간편가입_제로백H종신보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2208A02</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22082</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2208A02</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22082</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2208A02</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22082</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2208A02</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22082</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00026_2208_간편가입_제로백H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2208_간편가입_제로백H종신보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>2208002</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>2208002</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>2208002</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>2208002</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">

--- a/output/upload/S00026_2208_간편가입_제로백H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2208_간편가입_제로백H종신보험_무배당.xlsx
@@ -1728,32 +1728,88 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2208A06</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2208006</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
+      <c r="J11" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
+      <c r="O11" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n"/>
-      <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
-      <c r="AA11" s="6" t="n"/>
+      <c r="X11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA11" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
       <c r="AD11" s="6" t="n"/>
@@ -1778,32 +1834,88 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2208A06</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2208006</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="J12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
+      <c r="O12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n"/>
-      <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
-      <c r="AA12" s="6" t="n"/>
+      <c r="X12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA12" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
       <c r="AD12" s="6" t="n"/>
@@ -1828,32 +1940,88 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2208A06</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2208006</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
-      <c r="AA13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
       <c r="AD13" s="6" t="n"/>
@@ -1878,32 +2046,88 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2208A06</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2208006</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
-      <c r="AA14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AA14" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
       <c r="AD14" s="6" t="n"/>

--- a/output/upload/S00026_2208_간편가입_제로백H종신보험_무배당.xlsx
+++ b/output/upload/S00026_2208_간편가입_제로백H종신보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1339,7 +1339,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J7" s="6" t="n">
         <v>15</v>
       </c>
@@ -1445,7 +1449,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J8" s="6" t="n">
         <v>15</v>
       </c>
@@ -1518,22 +1526,22 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2208A02</t>
+          <t>2208A06</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>2208002</t>
+          <t>2208006</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1551,7 +1559,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J9" s="6" t="n">
         <v>15</v>
       </c>
@@ -1624,22 +1636,22 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2208A02</t>
+          <t>2208A06</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>2208002</t>
+          <t>2208006</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 1종(해약환급금 일부지급형Ⅰ)</t>
+          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1657,7 +1669,11 @@
           <t>99991231</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J10" s="6" t="n">
         <v>15</v>
       </c>
@@ -1728,88 +1744,32 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2208A06</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2208006</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA11" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
+      <c r="Z11" s="6" t="n"/>
+      <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
       <c r="AD11" s="6" t="n"/>
@@ -1834,88 +1794,32 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2208A06</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2208006</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z12" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
+      <c r="Z12" s="6" t="n"/>
+      <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
       <c r="AD12" s="6" t="n"/>
@@ -1940,88 +1844,32 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2208A06</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2208006</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y13" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z13" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="X13" s="6" t="n"/>
+      <c r="Y13" s="6" t="n"/>
+      <c r="Z13" s="6" t="n"/>
+      <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
       <c r="AD13" s="6" t="n"/>
@@ -2046,88 +1894,32 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2208A06</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2208006</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>한화생명 간편가입 제로백H종신보험 무배당 보장형 계약 2종(해약환급금 일부지급형Ⅱ)</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="n"/>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y14" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z14" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="X14" s="6" t="n"/>
+      <c r="Y14" s="6" t="n"/>
+      <c r="Z14" s="6" t="n"/>
+      <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
       <c r="AD14" s="6" t="n"/>
